--- a/artfynd/A 36508-2024 artfynd.xlsx
+++ b/artfynd/A 36508-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>119895961</v>
       </c>
       <c r="B3" t="n">
-        <v>82305</v>
+        <v>82321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 36508-2024 artfynd.xlsx
+++ b/artfynd/A 36508-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>119895961</v>
       </c>
       <c r="B3" t="n">
-        <v>82432</v>
+        <v>82433</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 36508-2024 artfynd.xlsx
+++ b/artfynd/A 36508-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>119895961</v>
       </c>
       <c r="B3" t="n">
-        <v>82433</v>
+        <v>82438</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 36508-2024 artfynd.xlsx
+++ b/artfynd/A 36508-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>119895961</v>
       </c>
       <c r="B3" t="n">
-        <v>82438</v>
+        <v>82439</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,11 +794,6 @@
       </c>
       <c r="E3" t="n">
         <v>1312</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 36508-2024 artfynd.xlsx
+++ b/artfynd/A 36508-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>119895961</v>
       </c>
       <c r="B3" t="n">
-        <v>82439</v>
+        <v>82443</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,6 +794,11 @@
       </c>
       <c r="E3" t="n">
         <v>1312</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 36508-2024 artfynd.xlsx
+++ b/artfynd/A 36508-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>119895961</v>
       </c>
       <c r="B3" t="n">
-        <v>82443</v>
+        <v>82444</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 36508-2024 artfynd.xlsx
+++ b/artfynd/A 36508-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>119895961</v>
       </c>
       <c r="B3" t="n">
-        <v>82444</v>
+        <v>82447</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
